--- a/artfynd/A 17981-2025 artfynd.xlsx
+++ b/artfynd/A 17981-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125406288</v>
+        <v>125406332</v>
       </c>
       <c r="B2" t="n">
-        <v>57995</v>
+        <v>57532</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,31 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103018</v>
+        <v>102977</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -789,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125406332</v>
+        <v>125406312</v>
       </c>
       <c r="B3" t="n">
-        <v>57532</v>
+        <v>57761</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -801,25 +793,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102977</v>
+        <v>103012</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -895,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125406307</v>
+        <v>125406325</v>
       </c>
       <c r="B4" t="n">
-        <v>57666</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,28 +903,24 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
@@ -1005,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125406312</v>
+        <v>125406288</v>
       </c>
       <c r="B5" t="n">
-        <v>57761</v>
+        <v>57995</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1021,27 +1009,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103012</v>
+        <v>103018</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1111,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125406325</v>
+        <v>125406307</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>57666</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1127,24 +1123,28 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>

--- a/artfynd/A 17981-2025 artfynd.xlsx
+++ b/artfynd/A 17981-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125406332</v>
+        <v>125406307</v>
       </c>
       <c r="B2" t="n">
-        <v>57532</v>
+        <v>57793</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,28 +687,32 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102977</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
@@ -781,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125406312</v>
+        <v>125406332</v>
       </c>
       <c r="B3" t="n">
-        <v>57761</v>
+        <v>57629</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,25 +797,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103012</v>
+        <v>102977</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -887,10 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125406325</v>
+        <v>125406312</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>57914</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,21 +907,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103012</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -993,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125406288</v>
+        <v>125406325</v>
       </c>
       <c r="B5" t="n">
-        <v>57995</v>
+        <v>57632</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,35 +1013,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103018</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1107,10 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125406307</v>
+        <v>125406288</v>
       </c>
       <c r="B6" t="n">
-        <v>57666</v>
+        <v>58111</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,21 +1119,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>103018</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1147,7 +1143,11 @@
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>

--- a/artfynd/A 17981-2025 artfynd.xlsx
+++ b/artfynd/A 17981-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125406307</v>
+        <v>125406312</v>
       </c>
       <c r="B2" t="n">
-        <v>57793</v>
+        <v>57914</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,28 +691,24 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>103012</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Bechstein, 1793)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
@@ -891,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125406312</v>
+        <v>125406325</v>
       </c>
       <c r="B4" t="n">
-        <v>57914</v>
+        <v>57632</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -907,21 +903,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103012</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -997,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125406325</v>
+        <v>125406288</v>
       </c>
       <c r="B5" t="n">
-        <v>57632</v>
+        <v>58111</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1013,27 +1009,35 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103018</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1103,10 +1107,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125406288</v>
+        <v>125406307</v>
       </c>
       <c r="B6" t="n">
-        <v>58111</v>
+        <v>57793</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1119,21 +1123,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103018</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1143,11 +1147,7 @@
       </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>

--- a/artfynd/A 17981-2025 artfynd.xlsx
+++ b/artfynd/A 17981-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125406312</v>
+        <v>125406325</v>
       </c>
       <c r="B2" t="n">
-        <v>57914</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103012</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsångare</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phylloscopus sibilatrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Bechstein, 1793)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -781,40 +776,39 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125406332</v>
+        <v>125406307</v>
       </c>
       <c r="B3" t="n">
-        <v>57629</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57811</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102977</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
@@ -887,15 +881,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125406325</v>
+        <v>125406312</v>
       </c>
       <c r="B4" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57932</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,21 +892,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103012</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsångare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phylloscopus sibilatrix</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bechstein, 1793)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -996,12 +985,7 @@
         <v>125406288</v>
       </c>
       <c r="B5" t="n">
-        <v>58111</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58129</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1107,44 +1091,35 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125406307</v>
+        <v>125406332</v>
       </c>
       <c r="B6" t="n">
-        <v>57793</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57645</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>102977</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>

--- a/artfynd/A 17981-2025 artfynd.xlsx
+++ b/artfynd/A 17981-2025 artfynd.xlsx
@@ -884,7 +884,7 @@
         <v>125406312</v>
       </c>
       <c r="B4" t="n">
-        <v>57932</v>
+        <v>57933</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         <v>125406288</v>
       </c>
       <c r="B5" t="n">
-        <v>58129</v>
+        <v>58130</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 17981-2025 artfynd.xlsx
+++ b/artfynd/A 17981-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1190,6 +1190,112 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126017886</v>
+      </c>
+      <c r="B7" t="n">
+        <v>57598</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100082</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Röd glada</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Milvus milvus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Rovfågelbo, Hl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>321967</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6371680</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kungsbacka</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vallda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ett rovfågelbo, troligen röd Glada som jag såg flyga i närheten, men Fiskgjuse läte har observerats och spelats in vid platsen flera ggr.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lottis Hörting</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lottis Hörting</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17981-2025 artfynd.xlsx
+++ b/artfynd/A 17981-2025 artfynd.xlsx
@@ -1195,7 +1195,7 @@
         <v>126017886</v>
       </c>
       <c r="B7" t="n">
-        <v>57598</v>
+        <v>57600</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 17981-2025 artfynd.xlsx
+++ b/artfynd/A 17981-2025 artfynd.xlsx
@@ -1195,7 +1195,7 @@
         <v>126017886</v>
       </c>
       <c r="B7" t="n">
-        <v>57600</v>
+        <v>57603</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 17981-2025 artfynd.xlsx
+++ b/artfynd/A 17981-2025 artfynd.xlsx
@@ -1195,7 +1195,7 @@
         <v>126017886</v>
       </c>
       <c r="B7" t="n">
-        <v>57603</v>
+        <v>57609</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 17981-2025 artfynd.xlsx
+++ b/artfynd/A 17981-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,11 +678,11 @@
         <v>125406325</v>
       </c>
       <c r="B2" t="n">
-        <v>57648</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -776,39 +776,35 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125406307</v>
+        <v>125406332</v>
       </c>
       <c r="B3" t="n">
-        <v>57811</v>
+        <v>57947</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>102977</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gröngöling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picus viridis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
@@ -884,7 +880,7 @@
         <v>125406312</v>
       </c>
       <c r="B4" t="n">
-        <v>57933</v>
+        <v>58238</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,11 +981,11 @@
         <v>125406288</v>
       </c>
       <c r="B5" t="n">
-        <v>58130</v>
+        <v>58439</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1091,35 +1087,39 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125406332</v>
+        <v>125406307</v>
       </c>
       <c r="B6" t="n">
-        <v>57645</v>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102977</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gröngöling</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picus viridis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
@@ -1190,112 +1190,6 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>126017886</v>
-      </c>
-      <c r="B7" t="n">
-        <v>57609</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>100082</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Röd glada</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Milvus milvus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Rovfågelbo, Hl</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>321967</v>
-      </c>
-      <c r="R7" t="n">
-        <v>6371680</v>
-      </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Halland</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Kungsbacka</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Halland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Vallda</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2025-06-16</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2025-06-16</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ett rovfågelbo, troligen röd Glada som jag såg flyga i närheten, men Fiskgjuse läte har observerats och spelats in vid platsen flera ggr.</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Lottis Hörting</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Lottis Hörting</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 17981-2025 artfynd.xlsx
+++ b/artfynd/A 17981-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125406325</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125406332</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125406312</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,6 +1104,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125406288</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1189,8 +1214,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125406307</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>